--- a/nail_artist_forms/001_nail_polish_durability_expectation_survey--nail_artist_forms.xlsx
+++ b/nail_artist_forms/001_nail_polish_durability_expectation_survey--nail_artist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>polish_wear_time</t>
+          <t>streaking_frequency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>How often polish lasts on your nails</t>
+          <t>How often do you notice streaks with this polish?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quality_assurance</t>
+          <t>overall_quality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How would you rate the quality of the polish?</t>
+          <t>How would you rate the overall quality of the polish?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nail_strengthening</t>
+          <t>nail_polish_duration</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How much does it strengthen your nails?</t>
+          <t>How long does it last on your nails?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>wear_quality</t>
+          <t>nail_strengthening</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How would you rate the wear quality?</t>
+          <t>How much does it strengthen your nails?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nail_streaking</t>
+          <t>color_durability</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How often do you notice streaks with this polish?</t>
+          <t>How would you rate the color durability?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>polish_color_durability</t>
+          <t>reapply_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How would you rate the color durability?</t>
+          <t>How often do you reapply this polish?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>overall_quality</t>
+          <t>wear_quality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Overall quality of the polish?</t>
+          <t>How would you rate the wear quality?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nail_strengthening_duration</t>
+          <t>nail_strengthening_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How long does it last on your nails?</t>
+          <t>Nail Strengthening 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>polish_wear_time_2</t>
+          <t>quality_assurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How often polish lasts on your nails 2?</t>
+          <t>How would you rate the quality of the polish?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,366 +722,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nail_strengthening_duration_2</t>
+          <t>overall_quality_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How long does it last on your nails 2?</t>
+          <t>Overall quality?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>nail_strengthening_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>How much does it strengthen your nails 2?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>quality_assurance_2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>How would you rate the quality of the polish 2?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>polish_color_durability_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>How would you rate the color durability 2?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>overall_quality_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Overall quality 2?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>wear_quality_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>How would you rate the wear quality 2?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nail_streaking_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>How often do you notice streaks with this polish 2?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>nail_strength_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>How much does it strengthen your nails 2?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>polish_strengthening_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How much does it strengthen your nails?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>streaking_frequency</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How often do you notice streaks with this polish?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>polish_durability_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How would you rate the color durability 3?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>overall_quality_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Overall quality 3?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>quality_assurance_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How would you rate the quality of the polish 3?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>color_durability_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How would you rate the color durability?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>wear_quality_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How would you rate the wear quality 3?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>nail_strengthening_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How much does it strengthen your nails 3?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +753,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,340 +781,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>polish_wear_time_choices</t>
+          <t>streaking_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nail</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nail</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>polish_wear_time_choices</t>
+          <t>streaking_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>polish</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wear_quality_choices</t>
+          <t>streaking_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_satisfied</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>wear_quality_choices</t>
+          <t>overall_quality_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>slightly_satisfied</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slightly satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wear_quality_choices</t>
+          <t>overall_quality_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>slightly_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Slightly satisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>wear_quality_choices</t>
+          <t>overall_quality_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>polish_color_durability_choices</t>
+          <t>overall_quality_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_satisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>polish_color_durability_choices</t>
+          <t>color_durability_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>slightly_satisfied</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Slightly satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>polish_color_durability_choices</t>
+          <t>color_durability_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>slightly_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Slightly satisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>polish_color_durability_choices</t>
+          <t>color_durability_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>overall_quality_choices</t>
+          <t>color_durability_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_satisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>overall_quality_choices</t>
+          <t>reapply_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>slightly_satisfied</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slightly satisfied</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>overall_quality_choices</t>
+          <t>reapply_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>overall_quality_choices</t>
+          <t>reapply_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>polish_wear_time_2_choices</t>
+          <t>wear_quality_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nail</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nail</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>polish_wear_time_2_choices</t>
+          <t>wear_quality_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>polish</t>
+          <t>slightly_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Slightly satisfied</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>polish_color_durability_2_choices</t>
+          <t>wear_quality_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_satisfied</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>polish_color_durability_2_choices</t>
+          <t>wear_quality_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>slightly_satisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slightly satisfied</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>polish_color_durability_2_choices</t>
+          <t>overall_quality_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>polish_color_durability_2_choices</t>
+          <t>overall_quality_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>slightly_satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>Slightly satisfied</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>not_satisfied</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Not satisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1488,418 +1143,10 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>slightly_satisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>Slightly satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>overall_quality_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>overall_quality_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Very satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>wear_quality_2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Not satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>wear_quality_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>slightly_satisfied</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Slightly satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>wear_quality_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>wear_quality_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Very satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>streaking_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>nail</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nail</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>streaking_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>polish</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Polish</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>polish_durability_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Not satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>polish_durability_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>slightly_satisfied</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Slightly satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>polish_durability_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>polish_durability_3_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Very satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>overall_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Not satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>overall_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>slightly_satisfied</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Slightly satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>overall_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>overall_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Very satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>color_durability_3_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Not satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>color_durability_3_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>slightly_satisfied</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Slightly satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>color_durability_3_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>color_durability_3_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Very satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>wear_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>not_satisfied</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Not satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>wear_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>slightly_satisfied</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Slightly satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>wear_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>wear_quality_3_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
         <is>
           <t>Very satisfied</t>
         </is>
